--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.5.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.5.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.5.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.5.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.5.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 000 Exposure Threats â€” Asserts She Knew</t>
+          <t>L402: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œpngeerâ€�â–</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 2</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -700,12 +704,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 4.â€”Susie Lange-</t>
+          <t>L404: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: “pngeer”■</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -779,12 +783,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -830,12 +834,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -858,12 +862,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE LEADING BREAKFAST FOOD â€”</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Wear the Tango, itâ€™s the very latest</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -933,12 +937,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CREMALT BREAD â€”" The Oval Loaf "</t>
+          <t>L581: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: shape, and itâ€™s a comfortable Collar</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -950,7 +954,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -1006,14 +1010,10 @@
           <t>L368: suspicious token(s): new5 (letter/digit mix) :: on our mailing list for our new5</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Extortion Victim is Hoeâ€™s</t>
+          <t>L362: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Third Issue Tomorrow•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1081,14 +1081,10 @@
           <t>L375: suspicious token(s): YOUR1 (letter/digit mix) :: : Call at our office for YOUR1</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L405: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 70 @Â° â€œ "s</t>
+          <t>L365: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: especially such matters of cur-■</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1152,14 +1148,10 @@
           <t>L376: line starts with digit/letter garbage token | suspicious token(s): 1copy (letter/digit mix) :: 1copy to-morrow morning. Or is</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L367: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Provinces, should have his name©</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1171,7 +1163,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1223,14 +1215,10 @@
           <t>L377: line starts with digit/letter garbage token | suspicious token(s): 4if (letter/digit mix) :: 4if this is not convenient, send F.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L541: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Apohaqui, Aug. 4.â€” Lightning has</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 000 by Exposure Threatsâ€”Asserts She Knew</t>
+          <t>L371: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: -Our third issue comes out to-■</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1269,7 +1257,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1286,14 +1274,10 @@
           <t>L378: suspicious token(s): see2 (letter/digit mix) :: nthe coupon and we shall see2</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L558: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: 3 Pairs of Men's Fine Cotton Hose for . . .â€¦</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: He Could not Marryâ€”Denies Contract to Pay</t>
+          <t>L707: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1305,7 +1289,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1327,7 +1311,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1349,16 +1333,8 @@
           <t>L405: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aXsetiEsI382 (letter/digit mix) :: aXsetiEsI382</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L581: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The â€” is the newest and, as yet.</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1413,11 +1389,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: unimitated wide sweeping front effectâ€”the</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1472,11 +1444,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Spring and Summer seasonâ€™s collar-find.</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1531,16 +1499,12 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: This Store will close every Thursday at one oâ€™clock.</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L277: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1590,11 +1554,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 4â€”Charging that</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1649,11 +1609,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mr. Hoeâ€™s answer in part says:</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1696,11 +1652,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: licly exposed as one of the plaintiffâ€™s</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1743,11 +1695,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MISS MORGAN, â€” York Street</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1786,11 +1734,7 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: world. Another of Li Sum-Lingâ€™s</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1829,11 +1773,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: COLGATE'Sâ€”Violet, Dactylis, Cashmere Bouquet, Eclat.</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1872,11 +1812,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WILLIAMSâ€™-Karsi, Violet, Carnation.</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1915,11 +1851,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NYAL'Sâ€” Red Rose, Violet.</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -1958,11 +1890,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L295: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ryanâ€™s Drug Store, Corn aand</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2001,11 +1929,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L333: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Mackintoshâ€˜s</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2044,11 +1968,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: THE LEADING BREAKFAST FOODâ€”</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2083,11 +2003,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CREMALT BREA Dâ€”"The Oval Loaf"</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2122,16 +2038,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜PHONE 41-41. REGENT ST .T</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L402: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2161,11 +2073,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Third Issue Tomorrowâ€¢</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2200,16 +2108,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Provinces, should have his nameÂ©</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L405: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L404: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2239,16 +2143,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - be of increased interest andâ€”</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2278,16 +2178,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L391: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 219-31</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L407: isolated marker/symbol line :: 3</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -2317,16 +2213,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L402: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: herself with men and persons gener- Bridgetâ€™s Academy, that the jewelry</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L527: isolated marker/symbol line :: a</t>
+          <t>L407: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2356,16 +2248,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L438: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: :â€”nor do you incur any obliga-</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 7</t>
+          <t>L527: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2395,16 +2283,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L465: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 4.â€”Heartbroken</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L581: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L580: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2434,21 +2318,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "My Dear Father and Mother:â€”My</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L582: isolated marker/symbol line :: 6</t>
+          <t>L581: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L707: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2473,14 +2353,14 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "P. S.â€”I will soon meet Grace."</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>L582: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
           <t>L767: isolated marker/symbol line :: W</t>
@@ -2508,11 +2388,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L533: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tinsmith, the girlâ€™s father, said he</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr"/>
@@ -2543,11 +2419,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L535: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: his son of his daughterâ€™s death. He is</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr"/>
@@ -2567,192 +2439,6 @@
       <c r="X39" s="1" t="inlineStr"/>
       <c r="Y39" s="1" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 4.â€”Susie Lange-</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L549: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: i St. John, Aug. 5.â€”Much to the</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œraking after" with a one-horse rake</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Apohaqui, Aug. 4.â€”Lightning has</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: on Mr. Slaytonâ€™s two farms of</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
